--- a/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1024,6 +1024,844 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DownloadFragment</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>下载列表 Fragment，管理下载任务展示、进度、暂停/继续/删除</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:43]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>继承Fragment，下载Tab页面，支持进度回调和暂停/继续/删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>创建 Fragment 视图，初始化 RecyclerView 和适配器</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onCreateView:74]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>初始化下载列表RecyclerView和空状态提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>loadTasks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>从持久化文件加载下载任务列表</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;loadTasks:126]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>JSON反序列化恢复下载任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>autoStartPendingTasks</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>自动启动状态为"下载中"但尚未运行的任务</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;autoStartPendingTasks:121]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>恢复崩溃前正在下载的任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>onPauseResume</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>暂停/继续按钮点击回调</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onPauseResume:248]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>根据当前状态切换暂停/继续</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>onDelete</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>删除按钮点击回调，先暂停下载再删除</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onDelete:263]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>确认对话框后执行删除</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>pauseDownload</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>暂停指定任务的下载（创建取消标志文件）</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;pauseDownload:283]</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>写cancel文件 + 中断Python进程</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>resumeDownload</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>继续暂停的下载任务</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;resumeDownload:309]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>复用task中的url重新执行下载</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>deleteTask</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>删除下载任务及对应的文件</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;deleteTask:338]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>删除任务记录、进度文件、部分下载文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>executeDownload</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>在后台线程中执行实际下载，调用 Python 并轮询进度</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;executeDownload:387]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>使用线程池executor.submit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>startProgressPolling</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;, progressFilePath&lt;String&gt;, isDone&lt;boolean[]&gt;</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>每 500ms 读取一次进度文件，更新任务进度到 UI</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;startProgressPolling:494]</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Handler.postDelayed循环轮询</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>callDownloadWithProgress</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>url&lt;String&gt;, formatId&lt;String&gt;, outputDir&lt;String&gt;, cookies&lt;String&gt;, progressFile&lt;String&gt;, cancelFlag&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>调用 Python 的 downloadVideoWithProgress 函数</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;callDownloadWithProgress:577]</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>通过Chaquopy执行Python端下载</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>formatSpeed</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bytesPerSec&lt;double&gt;</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>格式化下载速度显示</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;formatSpeed:663]</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>单位自适应 B/KB/MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>formatEta</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>etaSeconds&lt;long&gt;</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>格式化剩余时间显示</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;formatEta:678]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>显示秒/分/时</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>addExternalTask</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>供外部调用的公开方法，将新任务添加到列表并立即执行下载</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;addExternalTask:690]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026年06月09日12时00分00秒</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>HomeFragment调用入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>DownloadFragment</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>下载列表Fragment，展示所有下载任务的状态和进度</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:22]</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，下载Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化下载列表RecyclerView和空状态提示</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onCreateView:35]</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时06分53秒</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>后续实现下载列表适配器和数据绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>DownloadFragment</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>下载列表Fragment，展示所有下载任务的状态和进度</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:22]</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，下载Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化下载列表RecyclerView和空状态提示</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onCreateView:35]</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时18分34秒</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>后续实现下载列表适配器和数据绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>DownloadFragment</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>下载列表Fragment，展示所有下载任务的状态和进度</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:22]</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，下载Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化下载列表RecyclerView和空状态提示</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onCreateView:35]</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月09日20时23分25秒</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>后续实现下载列表适配器和数据绑定</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1862,6 +1862,82 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>DownloadFragment</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>下载列表Fragment，展示所有下载任务的状态和进度</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:22]</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>继承Fragment，下载Tab页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>onCreateView</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>inflater&lt;LayoutInflater&gt;, container&lt;ViewGroup&gt;, savedInstanceState&lt;Bundle&gt;</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>创建Fragment视图，初始化下载列表RecyclerView和空状态提示</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onCreateView:35]</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026年06月13日15时22分55秒</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>后续实现下载列表适配器和数据绑定</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:22]</t>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment:51]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1935,6 +1935,132 @@
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>后续实现下载列表适配器和数据绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>onShare</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>分享已下载的文件，通过系统 Intent.ACTION_SEND 弹出应用选择器</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onShare:458]</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026年06月20日23时55分23秒</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>使用 FileProvider content:// URI 确保 Android 7.0+ 跨应用文件访问</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>getMimeType</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>fileName&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>根据文件名扩展名获取对应的 MIME 类型（用于分享 Intent）</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;getMimeType:1139]</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026年06月20日23时55分23秒</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>支持 mp4/mkv/webm/m4a/mp3/aac，未知返回*/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>getUriForFile</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>context&lt;Context&gt;, file&lt;File&gt;</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Uri</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>通过 FileProvider 为指定文件生成 content:// URI（跨应用文件分享）</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;getUriForFile:1158]</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026年06月20日23时55分23秒</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>基于 file_paths.xml 路径映射</t>
         </is>
       </c>
     </row>

--- a/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
+++ b/ProjectDescription/DownloadFragment_FunctionNameReg.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2064,258 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>onShare</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>task&lt;DownloadTask&gt;</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>分享已下载的文件，弹出选择对话框让用户选择"分享原视频"或"压缩后分享"</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;onShare:464]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026年06月21日21时35分00秒</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>新增选择对话框，支持压缩后分享避免微信压画质</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>shareFile</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>file&lt;File&gt;</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>通用文件分享方法，通过FileProvider生成content:// URI并调用系统Intent分享文件</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;shareFile:494]</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026年06月21日21时35分00秒</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>适用于分享原视频文件或压缩后的ZIP压缩包</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>compressAndShare</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>videoFile&lt;File&gt;</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>异步压缩视频并分享，在后台线程使用ZipOutputStream将视频压缩为ZIP包</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;compressAndShare:522]</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026年06月21日21时35分00秒</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>压缩包存放在缓存目录，系统会自动清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>compressFileToZip</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sourceFile&lt;File&gt;, zipFile&lt;File&gt;</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>void</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>将单个文件压缩为ZIP格式，使用ZipOutputStream并设置Deflater.DEFAULT_COMPRESSION</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;compressFileToZip:570]</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026年06月21日21时35分00秒</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8KB缓冲区读写，避免大文件OOM，throws IOException</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>getMimeType</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>fileName&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>根据文件名扩展名获取对应的MIME类型（用于分享Intent）</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;getMimeType:1246]</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026年06月21日21时35分00秒</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>新增zip类型支持：application/zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>getUriForFile</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>context&lt;Context&gt;, file&lt;File&gt;</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Uri</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>通过FileProvider为指定文件生成content:// URI（跨应用文件分享）</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>(Files/app/src/main/java/com/example/grayvideodl/ui/download/DownloadFragment.java)[DownloadFragment-&gt;getUriForFile:1263]</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026年06月21日21时35分00秒</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>基于file_paths.xml路径映射，新增cache-path支持缓存目录</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
